--- a/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:56</t>
+          <t>2026-09-21 23:12:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:56</t>
+          <t>2026-09-21 23:12:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:56</t>
+          <t>2026-09-21 23:12:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:57</t>
+          <t>2026-09-21 23:12:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:58</t>
+          <t>2026-09-21 23:12:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:59</t>
+          <t>2026-09-21 23:13:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 19:28:59</t>
+          <t>2026-09-21 23:13:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:57</t>
+          <t>2026-09-21 23:20:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:57</t>
+          <t>2026-09-21 23:20:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:57</t>
+          <t>2026-09-21 23:20:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:58</t>
+          <t>2026-09-21 23:20:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:59</t>
+          <t>2026-09-21 23:20:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 23:13:01</t>
+          <t>2026-09-21 23:20:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 23:13:01</t>
+          <t>2026-09-21 23:20:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:20</t>
+          <t>2026-09-21 23:55:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.04%243,000</t>
+          <t>3.13%243,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:20</t>
+          <t>2026-09-21 23:55:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.77%212,000</t>
+          <t>2.84%212,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:20</t>
+          <t>2026-09-21 23:55:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.74%406,000</t>
+          <t>2.73%406,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.06%441,000</t>
+          <t>2.09%441,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.52%88,100</t>
+          <t>1.56%88,100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.49%351,900</t>
+          <t>1.51%351,900</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.40%158,000</t>
+          <t>1.48%158,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.38%90,000</t>
+          <t>1.43%90,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:21</t>
+          <t>2026-09-21 23:55:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.36%519,000</t>
+          <t>1.39%519,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.23%1,665,000</t>
+          <t>1.33%1,665,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.03%348,000</t>
+          <t>1.05%348,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.87%83,000</t>
+          <t>0.90%83,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.83%7,445</t>
+          <t>0.87%7,445</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.80%106,000</t>
+          <t>0.83%106,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.75%130,000</t>
+          <t>0.81%130,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:22</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.70%41,000</t>
+          <t>0.73%41,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:24</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.62%7,234</t>
+          <t>0.63%7,234</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:24</t>
+          <t>2026-09-21 23:55:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.52%94,000</t>
+          <t>0.57%94,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1612,6 +1612,69 @@
         </is>
       </c>
       <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:55:15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6920LASERTEC CORP</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.49%22,600</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>22600</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
